--- a/static/data/source/unemployment_rate.xlsx
+++ b/static/data/source/unemployment_rate.xlsx
@@ -369,7 +369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A4:WJ56"/>
+  <dimension ref="A4:WK56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="4">
@@ -3413,6 +3413,11 @@
           <t>07/01/2026</t>
         </is>
       </c>
+      <c r="WK4" t="inlineStr">
+        <is>
+          <t>08/01/2026</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5241,6 +5246,9 @@
       <c r="WJ5">
         <v>4.1</v>
       </c>
+      <c r="WK5">
+        <v>4.1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7069,6 +7077,9 @@
       <c r="WJ6">
         <v>3.4</v>
       </c>
+      <c r="WK6">
+        <v>3.4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8897,6 +8908,9 @@
       <c r="WJ7">
         <v>4.3</v>
       </c>
+      <c r="WK7">
+        <v>4.3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10725,6 +10739,9 @@
       <c r="WJ8">
         <v>4.9</v>
       </c>
+      <c r="WK8">
+        <v>4.9</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12553,6 +12570,9 @@
       <c r="WJ9">
         <v>4</v>
       </c>
+      <c r="WK9">
+        <v>3.9</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14381,6 +14401,9 @@
       <c r="WJ10">
         <v>5.1</v>
       </c>
+      <c r="WK10">
+        <v>5.1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -16209,6 +16232,9 @@
       <c r="WJ11">
         <v>3.9</v>
       </c>
+      <c r="WK11">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -18037,6 +18063,9 @@
       <c r="WJ12">
         <v>5.2</v>
       </c>
+      <c r="WK12">
+        <v>5.1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -19865,6 +19894,9 @@
       <c r="WJ13">
         <v>4.8</v>
       </c>
+      <c r="WK13">
+        <v>4.7</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -21693,6 +21725,9 @@
       <c r="WJ14">
         <v>5.9</v>
       </c>
+      <c r="WK14">
+        <v>5.7</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -23521,6 +23556,9 @@
       <c r="WJ15">
         <v>4.6</v>
       </c>
+      <c r="WK15">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -25349,6 +25387,9 @@
       <c r="WJ16">
         <v>3.3</v>
       </c>
+      <c r="WK16">
+        <v>3.2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -27177,6 +27218,9 @@
       <c r="WJ17">
         <v>2.7</v>
       </c>
+      <c r="WK17">
+        <v>2.7</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -29005,6 +29049,9 @@
       <c r="WJ18">
         <v>3.6</v>
       </c>
+      <c r="WK18">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -30833,6 +30880,9 @@
       <c r="WJ19">
         <v>4.9</v>
       </c>
+      <c r="WK19">
+        <v>4.7</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -32661,6 +32711,9 @@
       <c r="WJ20">
         <v>3.3</v>
       </c>
+      <c r="WK20">
+        <v>3.3</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -34489,6 +34542,9 @@
       <c r="WJ21">
         <v>3.2</v>
       </c>
+      <c r="WK21">
+        <v>3.2</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -36317,6 +36373,9 @@
       <c r="WJ22">
         <v>3.8</v>
       </c>
+      <c r="WK22">
+        <v>3.8</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -38145,6 +38204,9 @@
       <c r="WJ23">
         <v>4.7</v>
       </c>
+      <c r="WK23">
+        <v>4.7</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -39973,6 +40035,9 @@
       <c r="WJ24">
         <v>4.4</v>
       </c>
+      <c r="WK24">
+        <v>4.2</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -41801,6 +41866,9 @@
       <c r="WJ25">
         <v>3.1</v>
       </c>
+      <c r="WK25">
+        <v>3.2</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -43629,6 +43697,9 @@
       <c r="WJ26">
         <v>4.2</v>
       </c>
+      <c r="WK26">
+        <v>4.1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -45457,6 +45528,9 @@
       <c r="WJ27">
         <v>4.4</v>
       </c>
+      <c r="WK27">
+        <v>4.3</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -47285,6 +47359,9 @@
       <c r="WJ28">
         <v>4.9</v>
       </c>
+      <c r="WK28">
+        <v>5</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -49113,6 +49190,9 @@
       <c r="WJ29">
         <v>4.3</v>
       </c>
+      <c r="WK29">
+        <v>4.4</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -50941,6 +51021,9 @@
       <c r="WJ30">
         <v>3.6</v>
       </c>
+      <c r="WK30">
+        <v>3.4</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -52769,6 +52852,9 @@
       <c r="WJ31">
         <v>3.6</v>
       </c>
+      <c r="WK31">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -54597,6 +54683,9 @@
       <c r="WJ32">
         <v>3.2</v>
       </c>
+      <c r="WK32">
+        <v>3.2</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -56425,6 +56514,9 @@
       <c r="WJ33">
         <v>2.9</v>
       </c>
+      <c r="WK33">
+        <v>2.9</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -58253,6 +58345,9 @@
       <c r="WJ34">
         <v>5</v>
       </c>
+      <c r="WK34">
+        <v>4.8</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -60081,6 +60176,9 @@
       <c r="WJ35">
         <v>2.8</v>
       </c>
+      <c r="WK35">
+        <v>2.8</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -61909,6 +62007,9 @@
       <c r="WJ36">
         <v>4.4</v>
       </c>
+      <c r="WK36">
+        <v>4.3</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -63737,6 +63838,9 @@
       <c r="WJ37">
         <v>4.8</v>
       </c>
+      <c r="WK37">
+        <v>4.7</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -65565,6 +65669,9 @@
       <c r="WJ38">
         <v>4.4</v>
       </c>
+      <c r="WK38">
+        <v>4.3</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -67393,6 +67500,9 @@
       <c r="WJ39">
         <v>3.6</v>
       </c>
+      <c r="WK39">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -69221,6 +69331,9 @@
       <c r="WJ40">
         <v>2.2</v>
       </c>
+      <c r="WK40">
+        <v>2.2</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -71049,6 +71162,9 @@
       <c r="WJ41">
         <v>3.4</v>
       </c>
+      <c r="WK41">
+        <v>3.3</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -72877,6 +72993,9 @@
       <c r="WJ42">
         <v>4.3</v>
       </c>
+      <c r="WK42">
+        <v>4.3</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -74705,6 +74824,9 @@
       <c r="WJ43">
         <v>5.2</v>
       </c>
+      <c r="WK43">
+        <v>5.1</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -76533,6 +76655,9 @@
       <c r="WJ44">
         <v>3.9</v>
       </c>
+      <c r="WK44">
+        <v>3.7</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -78361,6 +78486,9 @@
       <c r="WJ45">
         <v>3.9</v>
       </c>
+      <c r="WK45">
+        <v>3.7</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -80189,6 +80317,9 @@
       <c r="WJ46">
         <v>4.2</v>
       </c>
+      <c r="WK46">
+        <v>4.1</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -82017,6 +82148,9 @@
       <c r="WJ47">
         <v>2</v>
       </c>
+      <c r="WK47">
+        <v>2</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -83845,6 +83979,9 @@
       <c r="WJ48">
         <v>3.4</v>
       </c>
+      <c r="WK48">
+        <v>3.4</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -85673,6 +85810,9 @@
       <c r="WJ49">
         <v>4.5</v>
       </c>
+      <c r="WK49">
+        <v>4.4</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -87501,6 +87641,9 @@
       <c r="WJ50">
         <v>3.6</v>
       </c>
+      <c r="WK50">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -89329,6 +89472,9 @@
       <c r="WJ51">
         <v>2.6</v>
       </c>
+      <c r="WK51">
+        <v>2.6</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -91157,6 +91303,9 @@
       <c r="WJ52">
         <v>3.7</v>
       </c>
+      <c r="WK52">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -92985,6 +93134,9 @@
       <c r="WJ53">
         <v>5</v>
       </c>
+      <c r="WK53">
+        <v>4.9</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -94813,6 +94965,9 @@
       <c r="WJ54">
         <v>4.1</v>
       </c>
+      <c r="WK54">
+        <v>4</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -96641,6 +96796,9 @@
       <c r="WJ55">
         <v>3.3</v>
       </c>
+      <c r="WK55">
+        <v>3.2</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -98467,6 +98625,9 @@
         <v>3.2</v>
       </c>
       <c r="WJ56">
+        <v>3</v>
+      </c>
+      <c r="WK56">
         <v>3</v>
       </c>
     </row>
